--- a/all_sim/gpt_pet.xlsx
+++ b/all_sim/gpt_pet.xlsx
@@ -332,15 +332,15 @@
   <cols>
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.46164021164021163</v>
+        <v>0.7183201058201059</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.24735449735449735</v>
+        <v>0.5681216931216931</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.24735449735449735</v>
+        <v>0.6114821267260292</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.31878306878306883</v>
+        <v>0.6245078134613018</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.24735449735449735</v>
+        <v>0.6114821267260292</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.24735449735449735</v>
+        <v>0.6114821267260292</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.27116402116402116</v>
+        <v>0.6014911014911015</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.34070294784580496</v>
+        <v>0.5542800453514739</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.07936507936507937</v>
+        <v>0.49556489262371617</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.07936507936507937</v>
+        <v>0.4615575396825397</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.3452380952380953</v>
+        <v>0.6579131652661064</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.3452380952380953</v>
+        <v>0.6309523809523809</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.15238095238095242</v>
+        <v>0.5367167919799499</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.11851851851851854</v>
+        <v>0.532943469785575</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.1740740740740741</v>
+        <v>0.5592592592592592</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.0824561403508772</v>
+        <v>0.48025246041934105</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.09487179487179488</v>
+        <v>0.45368589743589743</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.13703703703703704</v>
+        <v>0.5422027290448344</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.08222222222222222</v>
+        <v>0.46156565656565657</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.14242424242424245</v>
+        <v>0.5071095571095572</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.35185185185185186</v>
+        <v>0.6759259259259259</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.2863636363636364</v>
+        <v>0.6431818181818182</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.26136363636363635</v>
+        <v>0.6306818181818181</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.09090909090909088</v>
+        <v>0.516042780748663</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.04545454545454544</v>
+        <v>0.49331550802139035</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.04545454545454544</v>
+        <v>0.49331550802139035</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.09090909090909088</v>
+        <v>0.516042780748663</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
@@ -535,34 +535,34 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9116161616161615</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9436507936507936</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9116161616161615</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9436507936507936</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9116161616161615</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.45535714285714285</v>
+        <v>0.6973755411255411</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.45535714285714285</v>
+        <v>0.6973755411255411</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.45535714285714285</v>
+        <v>0.6973755411255411</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.45535714285714285</v>
+        <v>0.6973755411255411</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.45535714285714285</v>
+        <v>0.6973755411255411</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.3589285714285714</v>
+        <v>0.6508928571428572</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.6041666666666667</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.035714285714285726</v>
+        <v>0.48559907834101385</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.467741935483871</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.467741935483871</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="9">
@@ -649,31 +649,31 @@
         <v>1.0</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -686,31 +686,31 @@
         <v>1.0</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.23333333333333334</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.039999999999999994</v>
+        <v>0.52</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.03333333333333334</v>
+        <v>0.40128205128205124</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.03333333333333334</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.03333333333333334</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.03333333333333334</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.03333333333333334</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.03333333333333334</v>
+        <v>0.35000000000000003</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.26515151515151514</v>
+        <v>0.6121675943104514</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.26515151515151514</v>
+        <v>0.6121675943104514</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.26515151515151514</v>
+        <v>0.6121675943104514</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.10774410774410775</v>
+        <v>0.5154105154105154</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.1031144781144781</v>
+        <v>0.49033274926132064</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.14709595959595959</v>
+        <v>0.5135479797979798</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.13952020202020202</v>
+        <v>0.509760101010101</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.13952020202020202</v>
+        <v>0.509760101010101</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.13952020202020202</v>
+        <v>0.509760101010101</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.13952020202020202</v>
+        <v>0.509760101010101</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.6767676767676768</v>
+        <v>0.8383838383838385</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.36447811447811446</v>
+        <v>0.6822390572390572</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.2803030303030303</v>
+        <v>0.6401515151515151</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.26136363636363635</v>
+        <v>0.6306818181818181</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.36818181818181817</v>
+        <v>0.6840909090909091</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.48863636363636365</v>
+        <v>0.7234848484848485</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.3568181818181818</v>
+        <v>0.6575757575757576</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.3568181818181818</v>
+        <v>0.6575757575757576</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.3568181818181818</v>
+        <v>0.6575757575757576</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.3568181818181818</v>
+        <v>0.6575757575757576</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.06944444444444445</v>
+        <v>0.4758986928104575</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
     </row>
     <row r="14">
@@ -837,28 +837,28 @@
         <v>1.0</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -871,31 +871,31 @@
         <v>1.0</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16">
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="B16" s="0" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="C16" s="0" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="C16" s="0" t="n">
-        <v>0.4285714285714286</v>
-      </c>
       <c r="D16" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.7857142857142858</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.7857142857142858</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.7857142857142858</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="18">
@@ -979,34 +979,34 @@
         </is>
       </c>
       <c r="B18" s="0" t="n">
-        <v>0.43145717496033453</v>
+        <v>0.701967119590259</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0.3209696282961471</v>
+        <v>0.6375490343315598</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.2755990233691878</v>
+        <v>0.6152769891620714</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>0.16411413427038143</v>
+        <v>0.5595345446126682</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>0.18445853129279577</v>
+        <v>0.5695019929191252</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>0.29706080074483815</v>
+        <v>0.634511708783634</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>0.3012202909832334</v>
+        <v>0.6458482407297119</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>0.3095007164302401</v>
+        <v>0.6500333770830445</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>0.2824254223251969</v>
+        <v>0.6364508064006937</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>0.2824254223251969</v>
+        <v>0.6364508064006937</v>
       </c>
     </row>
     <row r="19">
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>0.30000000000000004</v>
+        <v>0.65</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20">
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="B20" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="21">
@@ -1090,34 +1090,34 @@
         </is>
       </c>
       <c r="B21" s="0" t="n">
-        <v>0.9722222222222222</v>
+        <v>0.9861111111111112</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
       <c r="K21" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
     </row>
     <row r="22">
@@ -1127,34 +1127,34 @@
         </is>
       </c>
       <c r="B22" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="K22" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="23">
@@ -1164,34 +1164,34 @@
         </is>
       </c>
       <c r="B23" s="0" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.8506944444444444</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="H23" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="I23" s="0" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.8506944444444444</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.8506944444444444</v>
       </c>
       <c r="K23" s="0" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.8506944444444444</v>
       </c>
     </row>
     <row r="24">
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="B24" s="0" t="n">
-        <v>0.42919418821414196</v>
+        <v>0.7032334577434346</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>0.42919418821414196</v>
+        <v>0.7032334577434346</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.3312265985023042</v>
+        <v>0.6541190463775889</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>0.3312265985023042</v>
+        <v>0.6541190463775889</v>
       </c>
       <c r="F24" s="0" t="n">
-        <v>0.3312265985023042</v>
+        <v>0.6541190463775889</v>
       </c>
       <c r="G24" s="0" t="n">
-        <v>0.3220610325957413</v>
+        <v>0.6492658104155177</v>
       </c>
       <c r="H24" s="0" t="n">
-        <v>0.3264550931259601</v>
+        <v>0.6515996395862358</v>
       </c>
       <c r="I24" s="0" t="n">
-        <v>0.3264550931259601</v>
+        <v>0.6515996395862358</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>0.3264550931259601</v>
+        <v>0.6515996395862358</v>
       </c>
       <c r="K24" s="0" t="n">
-        <v>0.16103051629787066</v>
+        <v>0.5577879854216626</v>
       </c>
     </row>
     <row r="25">
@@ -1238,34 +1238,34 @@
         </is>
       </c>
       <c r="B25" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="G25" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="H25" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="I25" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="K25" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -1278,31 +1278,31 @@
         <v>1.0</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9583333333333333</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.9083333333333333</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.9083333333333333</v>
       </c>
       <c r="F26" s="0" t="n">
-        <v>0.55</v>
+        <v>0.775</v>
       </c>
       <c r="G26" s="0" t="n">
-        <v>0.55</v>
+        <v>0.775</v>
       </c>
       <c r="H26" s="0" t="n">
-        <v>0.55</v>
+        <v>0.775</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>0.55</v>
+        <v>0.775</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>0.55</v>
+        <v>0.775</v>
       </c>
       <c r="K26" s="0" t="n">
-        <v>0.55</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="27">
@@ -1312,34 +1312,34 @@
         </is>
       </c>
       <c r="B27" s="0" t="n">
-        <v>0.1677045177045177</v>
+        <v>0.4876984126984127</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>0.25728530728530724</v>
+        <v>0.515739427836202</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0.09840159840159841</v>
+        <v>0.41684785802432867</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>0.04738356881214024</v>
+        <v>0.38083464154892727</v>
       </c>
       <c r="F27" s="0" t="n">
-        <v>0.05287807430664573</v>
+        <v>0.37454030297610763</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>0.046268315018315014</v>
+        <v>0.35240245019208427</v>
       </c>
       <c r="H27" s="0" t="n">
-        <v>0.034119801766860594</v>
+        <v>0.3238780827016121</v>
       </c>
       <c r="I27" s="0" t="n">
-        <v>0.034119801766860594</v>
+        <v>0.2920599008834303</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>0.03625228937728938</v>
+        <v>0.31382506941982746</v>
       </c>
       <c r="K27" s="0" t="n">
-        <v>0.014906043389015525</v>
+        <v>0.2574530216945078</v>
       </c>
     </row>
     <row r="28">
@@ -1349,34 +1349,34 @@
         </is>
       </c>
       <c r="B28" s="0" t="n">
-        <v>0.40212368683383176</v>
+        <v>0.6740348163898888</v>
       </c>
       <c r="C28" s="0" t="n">
-        <v>0.4322162794264243</v>
+        <v>0.6878062529207594</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>0.4119750298011168</v>
+        <v>0.6917018006148441</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>0.4119750298011168</v>
+        <v>0.7013146177042967</v>
       </c>
       <c r="F28" s="0" t="n">
-        <v>0.05594722626928746</v>
+        <v>0.4664351515961822</v>
       </c>
       <c r="G28" s="0" t="n">
-        <v>0.05163320333188888</v>
+        <v>0.46899841984776264</v>
       </c>
       <c r="H28" s="0" t="n">
-        <v>0.46002856376044776</v>
+        <v>0.7098122616782037</v>
       </c>
       <c r="I28" s="0" t="n">
-        <v>0.1400918257802316</v>
+        <v>0.4569506747948777</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>0.1400918257802316</v>
+        <v>0.4569506747948777</v>
       </c>
       <c r="K28" s="0" t="n">
-        <v>0.1490251897860594</v>
+        <v>0.4600547635677285</v>
       </c>
     </row>
     <row r="29">
@@ -1386,34 +1386,34 @@
         </is>
       </c>
       <c r="B29" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C29" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F29" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H29" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I29" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K29" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="30">
@@ -1429,28 +1429,28 @@
         <v>1.0</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>0.8819444444444444</v>
+        <v>0.9409722222222222</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>0.8819444444444444</v>
+        <v>0.9409722222222222</v>
       </c>
       <c r="F30" s="0" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="G30" s="0" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="H30" s="0" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="I30" s="0" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="J30" s="0" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="K30" s="0" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.7888888888888889</v>
       </c>
     </row>
     <row r="31">
@@ -1460,34 +1460,34 @@
         </is>
       </c>
       <c r="B31" s="0" t="n">
-        <v>0.1748971193415638</v>
+        <v>0.48744855967078193</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>0.15990593768371544</v>
+        <v>0.4819137531555832</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.13374485596707822</v>
+        <v>0.4668724279835391</v>
       </c>
       <c r="E31" s="0" t="n">
-        <v>0.13374485596707822</v>
+        <v>0.4668724279835391</v>
       </c>
       <c r="F31" s="0" t="n">
-        <v>0.13168724279835395</v>
+        <v>0.465843621399177</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>0.13168724279835395</v>
+        <v>0.465843621399177</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>0.13168724279835395</v>
+        <v>0.465843621399177</v>
       </c>
       <c r="I31" s="0" t="n">
-        <v>0.13168724279835395</v>
+        <v>0.465843621399177</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>0.13168724279835395</v>
+        <v>0.465843621399177</v>
       </c>
       <c r="K31" s="0" t="n">
-        <v>0.13168724279835395</v>
+        <v>0.465843621399177</v>
       </c>
     </row>
     <row r="32">
@@ -1497,34 +1497,34 @@
         </is>
       </c>
       <c r="B32" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="C32" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="E32" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="F32" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="G32" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="H32" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="I32" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="K32" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="33">
@@ -1534,34 +1534,34 @@
         </is>
       </c>
       <c r="B33" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.399671052631579</v>
       </c>
       <c r="C33" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.399671052631579</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.40625</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.40625</v>
       </c>
       <c r="F33" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.40625</v>
       </c>
       <c r="G33" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.40625</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.40625</v>
       </c>
       <c r="I33" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.40625</v>
       </c>
       <c r="J33" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.40625</v>
       </c>
       <c r="K33" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.40625</v>
       </c>
     </row>
     <row r="34">
@@ -1577,28 +1577,28 @@
         <v>1.0</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>0.5766850048100048</v>
+        <v>0.7883425024050024</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>0.2883425024050024</v>
+        <v>0.6441712512025012</v>
       </c>
       <c r="F34" s="0" t="n">
-        <v>0.2883425024050024</v>
+        <v>0.6441712512025012</v>
       </c>
       <c r="G34" s="0" t="n">
-        <v>0.26741747835497837</v>
+        <v>0.6337087391774892</v>
       </c>
       <c r="H34" s="0" t="n">
-        <v>0.47513189935064926</v>
+        <v>0.7375659496753246</v>
       </c>
       <c r="I34" s="0" t="n">
-        <v>0.47513189935064926</v>
+        <v>0.7375659496753246</v>
       </c>
       <c r="J34" s="0" t="n">
-        <v>0.4535684223184224</v>
+        <v>0.7267842111592112</v>
       </c>
       <c r="K34" s="0" t="n">
-        <v>0.5902856691919189</v>
+        <v>0.7747346713306533</v>
       </c>
     </row>
     <row r="35">
@@ -1608,34 +1608,34 @@
         </is>
       </c>
       <c r="B35" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.792016806722689</v>
       </c>
       <c r="C35" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.792016806722689</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7324929971988796</v>
       </c>
       <c r="E35" s="0" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7324929971988796</v>
       </c>
       <c r="F35" s="0" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7324929971988796</v>
       </c>
       <c r="G35" s="0" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7324929971988796</v>
       </c>
       <c r="H35" s="0" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7324929971988796</v>
       </c>
       <c r="I35" s="0" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7324929971988796</v>
       </c>
       <c r="J35" s="0" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7324929971988796</v>
       </c>
       <c r="K35" s="0" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7324929971988796</v>
       </c>
     </row>
     <row r="36">
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="B36" s="0" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.5341880341880342</v>
       </c>
       <c r="C36" s="0" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.5341880341880342</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.5341880341880342</v>
       </c>
       <c r="E36" s="0" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.5341880341880342</v>
       </c>
       <c r="F36" s="0" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.5341880341880342</v>
       </c>
       <c r="G36" s="0" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.5341880341880342</v>
       </c>
       <c r="H36" s="0" t="n">
-        <v>0.14814814814814814</v>
+        <v>0.4706257982120051</v>
       </c>
       <c r="I36" s="0" t="n">
-        <v>0.14814814814814814</v>
+        <v>0.4740740740740741</v>
       </c>
       <c r="J36" s="0" t="n">
-        <v>0.14814814814814814</v>
+        <v>0.4740740740740741</v>
       </c>
       <c r="K36" s="0" t="n">
-        <v>0.14814814814814814</v>
+        <v>0.4740740740740741</v>
       </c>
     </row>
     <row r="37">
@@ -1682,34 +1682,34 @@
         </is>
       </c>
       <c r="B37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="C37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="E37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="K37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="38">

--- a/all_sim/gpt_pet.xlsx
+++ b/all_sim/gpt_pet.xlsx
@@ -332,15 +332,15 @@
   <cols>
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="7" max="7" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.7183201058201059</v>
+        <v>0.4500992063492063</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.5681216931216931</v>
+        <v>0.21987066431510874</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.6114821267260292</v>
+        <v>0.24132146083365594</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.6245078134613018</v>
+        <v>0.29654238956564544</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.6114821267260292</v>
+        <v>0.24132146083365594</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.6114821267260292</v>
+        <v>0.24132146083365594</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.6014911014911015</v>
+        <v>0.25267556517556516</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.5542800453514739</v>
+        <v>0.2616111920958859</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.49556489262371617</v>
+        <v>0.07236227824463119</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.4615575396825397</v>
+        <v>0.06696428571428573</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.6579131652661064</v>
+        <v>0.3350840336134454</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.316468253968254</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.5367167919799499</v>
+        <v>0.1403508771929825</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.532943469785575</v>
+        <v>0.112280701754386</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.5592592592592592</v>
+        <v>0.16440329218106997</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.48025246041934105</v>
+        <v>0.072400513478819</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.45368589743589743</v>
+        <v>0.07708333333333334</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.5422027290448344</v>
+        <v>0.1298245614035088</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.46156565656565657</v>
+        <v>0.06914141414141414</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.5071095571095572</v>
+        <v>0.1241647241647242</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.6759259259259259</v>
+        <v>0.35185185185185186</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.06666666666666665</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.6431818181818182</v>
+        <v>0.2863636363636364</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.6306818181818181</v>
+        <v>0.26136363636363635</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.516042780748663</v>
+        <v>0.08556149732620319</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.49331550802139035</v>
+        <v>0.042780748663101595</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.49331550802139035</v>
+        <v>0.042780748663101595</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.516042780748663</v>
+        <v>0.08556149732620319</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -535,34 +535,34 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.9116161616161615</v>
+        <v>0.8299663299663299</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.48611111111111116</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.5347222222222223</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.9436507936507936</v>
+        <v>0.8904761904761904</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.9116161616161615</v>
+        <v>0.8299663299663299</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.9436507936507936</v>
+        <v>0.8904761904761904</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.9116161616161615</v>
+        <v>0.8299663299663299</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.6973755411255411</v>
+        <v>0.4277597402597403</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.6973755411255411</v>
+        <v>0.4277597402597403</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.6973755411255411</v>
+        <v>0.4277597402597403</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.6973755411255411</v>
+        <v>0.4277597402597403</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.6973755411255411</v>
+        <v>0.4277597402597403</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.6508928571428572</v>
+        <v>0.3384183673469387</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.5664062500000001</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.48559907834101385</v>
+        <v>0.03341013824884794</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.467741935483871</v>
+        <v>0.0</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.467741935483871</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -649,31 +649,31 @@
         <v>1.0</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="10">
@@ -686,31 +686,31 @@
         <v>1.0</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.52</v>
+        <v>0.039999999999999994</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.40128205128205124</v>
+        <v>0.025641025641025644</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.35000000000000003</v>
+        <v>0.02222222222222223</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.35000000000000003</v>
+        <v>0.02222222222222223</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.35000000000000003</v>
+        <v>0.02222222222222223</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.35000000000000003</v>
+        <v>0.02222222222222223</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.35000000000000003</v>
+        <v>0.02222222222222223</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.6121675943104514</v>
+        <v>0.2543290043290043</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.6121675943104514</v>
+        <v>0.2543290043290043</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.6121675943104514</v>
+        <v>0.2543290043290043</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.5154105154105154</v>
+        <v>0.09945609945609947</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.49033274926132064</v>
+        <v>0.09048821548821548</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.5135479797979798</v>
+        <v>0.12944444444444445</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.509760101010101</v>
+        <v>0.12277777777777778</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.509760101010101</v>
+        <v>0.12277777777777778</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.509760101010101</v>
+        <v>0.12277777777777778</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.509760101010101</v>
+        <v>0.12277777777777778</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.8383838383838385</v>
+        <v>0.6767676767676768</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.6822390572390572</v>
+        <v>0.36447811447811446</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.6401515151515151</v>
+        <v>0.2803030303030303</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.6306818181818181</v>
+        <v>0.26136363636363635</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.6840909090909091</v>
+        <v>0.36818181818181817</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.7234848484848485</v>
+        <v>0.4682765151515152</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.6575757575757576</v>
+        <v>0.3419507575757576</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.6575757575757576</v>
+        <v>0.3419507575757576</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.6575757575757576</v>
+        <v>0.3419507575757576</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.6575757575757576</v>
+        <v>0.3419507575757576</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.4758986928104575</v>
+        <v>0.06127450980392157</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
     </row>
     <row r="14">
@@ -837,28 +837,28 @@
         <v>1.0</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
     </row>
     <row r="15">
@@ -871,31 +871,31 @@
         <v>1.0</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.7857142857142858</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.7857142857142858</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.7857142857142858</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -979,34 +979,34 @@
         </is>
       </c>
       <c r="B18" s="0" t="n">
-        <v>0.701967119590259</v>
+        <v>0.4195822068421602</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0.6375490343315598</v>
+        <v>0.30624625085136975</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.6152769891620714</v>
+        <v>0.2631846529471523</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>0.5595345446126682</v>
+        <v>0.15672160569964352</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>0.5695019929191252</v>
+        <v>0.1760740525976687</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>0.634511708783634</v>
+        <v>0.2887319932473193</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>0.6458482407297119</v>
+        <v>0.2983515263072026</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>0.6500333770830445</v>
+        <v>0.3065808983507095</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>0.6364508064006937</v>
+        <v>0.2797356563982903</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>0.6364508064006937</v>
+        <v>0.2797356563982903</v>
       </c>
     </row>
     <row r="19">
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>0.65</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="20">
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="B20" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
     </row>
     <row r="21">
@@ -1090,34 +1090,34 @@
         </is>
       </c>
       <c r="B21" s="0" t="n">
-        <v>0.9861111111111112</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
       <c r="K21" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
     </row>
     <row r="22">
@@ -1127,34 +1127,34 @@
         </is>
       </c>
       <c r="B22" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="K22" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="23">
@@ -1164,34 +1164,34 @@
         </is>
       </c>
       <c r="B23" s="0" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="H23" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="I23" s="0" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="K23" s="0" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
     </row>
     <row r="24">
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="B24" s="0" t="n">
-        <v>0.7032334577434346</v>
+        <v>0.4194397748456387</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>0.7032334577434346</v>
+        <v>0.4194397748456387</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.6541190463775889</v>
+        <v>0.32361219393903284</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>0.6541190463775889</v>
+        <v>0.32361219393903284</v>
       </c>
       <c r="F24" s="0" t="n">
-        <v>0.6541190463775889</v>
+        <v>0.32361219393903284</v>
       </c>
       <c r="G24" s="0" t="n">
-        <v>0.6492658104155177</v>
+        <v>0.31448312594642974</v>
       </c>
       <c r="H24" s="0" t="n">
-        <v>0.6515996395862358</v>
+        <v>0.31886311421605407</v>
       </c>
       <c r="I24" s="0" t="n">
-        <v>0.6515996395862358</v>
+        <v>0.31886311421605407</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>0.6515996395862358</v>
+        <v>0.31886311421605407</v>
       </c>
       <c r="K24" s="0" t="n">
-        <v>0.5577879854216626</v>
+        <v>0.1537109473752402</v>
       </c>
     </row>
     <row r="25">
@@ -1238,34 +1238,34 @@
         </is>
       </c>
       <c r="B25" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G25" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="H25" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="I25" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="K25" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="26">
@@ -1278,31 +1278,31 @@
         <v>1.0</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>0.9583333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>0.9083333333333333</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>0.9083333333333333</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="F26" s="0" t="n">
-        <v>0.775</v>
+        <v>0.55</v>
       </c>
       <c r="G26" s="0" t="n">
-        <v>0.775</v>
+        <v>0.55</v>
       </c>
       <c r="H26" s="0" t="n">
-        <v>0.775</v>
+        <v>0.55</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>0.775</v>
+        <v>0.55</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>0.775</v>
+        <v>0.55</v>
       </c>
       <c r="K26" s="0" t="n">
-        <v>0.775</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="27">
@@ -1312,34 +1312,34 @@
         </is>
       </c>
       <c r="B27" s="0" t="n">
-        <v>0.4876984126984127</v>
+        <v>0.13545364891518738</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>0.515739427836202</v>
+        <v>0.19918862499507656</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0.41684785802432867</v>
+        <v>0.07235411647176354</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>0.38083464154892727</v>
+        <v>0.033845406294385885</v>
       </c>
       <c r="F27" s="0" t="n">
-        <v>0.37454030297610763</v>
+        <v>0.0368138492008293</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>0.35240245019208427</v>
+        <v>0.03046937818279281</v>
       </c>
       <c r="H27" s="0" t="n">
-        <v>0.3238780827016121</v>
+        <v>0.02093715108420991</v>
       </c>
       <c r="I27" s="0" t="n">
-        <v>0.2920599008834303</v>
+        <v>0.01876589097177333</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>0.31382506941982746</v>
+        <v>0.021439525975816297</v>
       </c>
       <c r="K27" s="0" t="n">
-        <v>0.2574530216945078</v>
+        <v>0.007453021694507763</v>
       </c>
     </row>
     <row r="28">
@@ -1349,34 +1349,34 @@
         </is>
       </c>
       <c r="B28" s="0" t="n">
-        <v>0.6740348163898888</v>
+        <v>0.38038727132930034</v>
       </c>
       <c r="C28" s="0" t="n">
-        <v>0.6878062529207594</v>
+        <v>0.4077512070060607</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>0.6917018006148441</v>
+        <v>0.400204314663942</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>0.7013146177042967</v>
+        <v>0.40812479587774186</v>
       </c>
       <c r="F28" s="0" t="n">
-        <v>0.4664351515961822</v>
+        <v>0.04906141380537516</v>
       </c>
       <c r="G28" s="0" t="n">
-        <v>0.46899841984776264</v>
+        <v>0.045765793862356054</v>
       </c>
       <c r="H28" s="0" t="n">
-        <v>0.7098122616782037</v>
+        <v>0.44144155108325794</v>
       </c>
       <c r="I28" s="0" t="n">
-        <v>0.4569506747948777</v>
+        <v>0.10840438899660779</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>0.4569506747948777</v>
+        <v>0.10840438899660779</v>
       </c>
       <c r="K28" s="0" t="n">
-        <v>0.4600547635677285</v>
+        <v>0.11491098971455183</v>
       </c>
     </row>
     <row r="29">
@@ -1386,34 +1386,34 @@
         </is>
       </c>
       <c r="B29" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="C29" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F29" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="H29" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I29" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="K29" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -1429,28 +1429,28 @@
         <v>1.0</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>0.9409722222222222</v>
+        <v>0.8819444444444444</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>0.9409722222222222</v>
+        <v>0.8819444444444444</v>
       </c>
       <c r="F30" s="0" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="G30" s="0" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="H30" s="0" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="I30" s="0" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="J30" s="0" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="K30" s="0" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.5777777777777777</v>
       </c>
     </row>
     <row r="31">
@@ -1460,34 +1460,34 @@
         </is>
       </c>
       <c r="B31" s="0" t="n">
-        <v>0.48744855967078193</v>
+        <v>0.13991769547325103</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>0.4819137531555832</v>
+        <v>0.12855183225553596</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.4668724279835391</v>
+        <v>0.10699588477366258</v>
       </c>
       <c r="E31" s="0" t="n">
-        <v>0.4668724279835391</v>
+        <v>0.10699588477366258</v>
       </c>
       <c r="F31" s="0" t="n">
-        <v>0.465843621399177</v>
+        <v>0.10534979423868317</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>0.465843621399177</v>
+        <v>0.10534979423868317</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>0.465843621399177</v>
+        <v>0.10534979423868317</v>
       </c>
       <c r="I31" s="0" t="n">
-        <v>0.465843621399177</v>
+        <v>0.10534979423868317</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>0.465843621399177</v>
+        <v>0.10534979423868317</v>
       </c>
       <c r="K31" s="0" t="n">
-        <v>0.465843621399177</v>
+        <v>0.10534979423868317</v>
       </c>
     </row>
     <row r="32">
@@ -1497,34 +1497,34 @@
         </is>
       </c>
       <c r="B32" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="C32" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E32" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F32" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="G32" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H32" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I32" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="K32" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="33">
@@ -1534,34 +1534,34 @@
         </is>
       </c>
       <c r="B33" s="0" t="n">
-        <v>0.399671052631579</v>
+        <v>0.04605263157894737</v>
       </c>
       <c r="C33" s="0" t="n">
-        <v>0.399671052631579</v>
+        <v>0.04605263157894737</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.40625</v>
+        <v>0.046875</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>0.40625</v>
+        <v>0.046875</v>
       </c>
       <c r="F33" s="0" t="n">
-        <v>0.40625</v>
+        <v>0.046875</v>
       </c>
       <c r="G33" s="0" t="n">
-        <v>0.40625</v>
+        <v>0.046875</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>0.40625</v>
+        <v>0.046875</v>
       </c>
       <c r="I33" s="0" t="n">
-        <v>0.40625</v>
+        <v>0.046875</v>
       </c>
       <c r="J33" s="0" t="n">
-        <v>0.40625</v>
+        <v>0.046875</v>
       </c>
       <c r="K33" s="0" t="n">
-        <v>0.40625</v>
+        <v>0.046875</v>
       </c>
     </row>
     <row r="34">
@@ -1577,28 +1577,28 @@
         <v>1.0</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>0.7883425024050024</v>
+        <v>0.5766850048100048</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>0.6441712512025012</v>
+        <v>0.2883425024050024</v>
       </c>
       <c r="F34" s="0" t="n">
-        <v>0.6441712512025012</v>
+        <v>0.2883425024050024</v>
       </c>
       <c r="G34" s="0" t="n">
-        <v>0.6337087391774892</v>
+        <v>0.26741747835497837</v>
       </c>
       <c r="H34" s="0" t="n">
-        <v>0.7375659496753246</v>
+        <v>0.47513189935064926</v>
       </c>
       <c r="I34" s="0" t="n">
-        <v>0.7375659496753246</v>
+        <v>0.47513189935064926</v>
       </c>
       <c r="J34" s="0" t="n">
-        <v>0.7267842111592112</v>
+        <v>0.4535684223184224</v>
       </c>
       <c r="K34" s="0" t="n">
-        <v>0.7747346713306533</v>
+        <v>0.5661923765718406</v>
       </c>
     </row>
     <row r="35">
@@ -1608,34 +1608,34 @@
         </is>
       </c>
       <c r="B35" s="0" t="n">
-        <v>0.792016806722689</v>
+        <v>0.6050420168067226</v>
       </c>
       <c r="C35" s="0" t="n">
-        <v>0.792016806722689</v>
+        <v>0.6050420168067226</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>0.7324929971988796</v>
+        <v>0.49299719887955185</v>
       </c>
       <c r="E35" s="0" t="n">
-        <v>0.7324929971988796</v>
+        <v>0.49299719887955185</v>
       </c>
       <c r="F35" s="0" t="n">
-        <v>0.7324929971988796</v>
+        <v>0.49299719887955185</v>
       </c>
       <c r="G35" s="0" t="n">
-        <v>0.7324929971988796</v>
+        <v>0.49299719887955185</v>
       </c>
       <c r="H35" s="0" t="n">
-        <v>0.7324929971988796</v>
+        <v>0.49299719887955185</v>
       </c>
       <c r="I35" s="0" t="n">
-        <v>0.7324929971988796</v>
+        <v>0.49299719887955185</v>
       </c>
       <c r="J35" s="0" t="n">
-        <v>0.7324929971988796</v>
+        <v>0.49299719887955185</v>
       </c>
       <c r="K35" s="0" t="n">
-        <v>0.7324929971988796</v>
+        <v>0.49299719887955185</v>
       </c>
     </row>
     <row r="36">
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="B36" s="0" t="n">
-        <v>0.5341880341880342</v>
+        <v>0.18803418803418803</v>
       </c>
       <c r="C36" s="0" t="n">
-        <v>0.5341880341880342</v>
+        <v>0.18803418803418803</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>0.5341880341880342</v>
+        <v>0.18803418803418803</v>
       </c>
       <c r="E36" s="0" t="n">
-        <v>0.5341880341880342</v>
+        <v>0.18803418803418803</v>
       </c>
       <c r="F36" s="0" t="n">
-        <v>0.5341880341880342</v>
+        <v>0.18803418803418803</v>
       </c>
       <c r="G36" s="0" t="n">
-        <v>0.5341880341880342</v>
+        <v>0.18803418803418803</v>
       </c>
       <c r="H36" s="0" t="n">
-        <v>0.4706257982120051</v>
+        <v>0.11749680715197956</v>
       </c>
       <c r="I36" s="0" t="n">
-        <v>0.4740740740740741</v>
+        <v>0.11851851851851852</v>
       </c>
       <c r="J36" s="0" t="n">
-        <v>0.4740740740740741</v>
+        <v>0.11851851851851852</v>
       </c>
       <c r="K36" s="0" t="n">
-        <v>0.4740740740740741</v>
+        <v>0.11851851851851852</v>
       </c>
     </row>
     <row r="37">
@@ -1682,34 +1682,34 @@
         </is>
       </c>
       <c r="B37" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="C37" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E37" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F37" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G37" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H37" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I37" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J37" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="K37" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38">
